--- a/artfynd/A 54020-2024 artfynd.xlsx
+++ b/artfynd/A 54020-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73727118</v>
+        <v>87517969</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,19 +713,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Körartorp, 620 meter ost om, Vstm</t>
+          <t>Körartorp, 600 m öster om, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505378.1711708493</v>
+        <v>505420</v>
       </c>
       <c r="R2" t="n">
-        <v>6611389.851046764</v>
+        <v>6611330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,24 +754,19 @@
           <t>Linde</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Lin-0029</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,41 +790,40 @@
           <t>Anita Lindgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73727104</v>
+        <v>103691457</v>
       </c>
       <c r="B3" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,27 +831,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Körartorp, 660 meter ost om, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505419.7892171047</v>
+        <v>505564</v>
       </c>
       <c r="R3" t="n">
-        <v>6611330.248087614</v>
+        <v>6611498</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,27 +873,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En av två växtplatser i närområdet.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,56 +897,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anita Lindgren</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87517969</v>
+        <v>129834380</v>
       </c>
       <c r="B4" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>245</v>
+        <v>100942</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -970,26 +950,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Körartorp, 600 m öster om, Vstm</t>
+          <t>Hinderbacken Yta 4:10 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505420.2957090242</v>
+        <v>505496</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330.248820866</v>
+        <v>6611414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,29 +992,14 @@
           <t>Linde</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>T-Lin-7025</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,9 +1008,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1057,48 +1034,43 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anita Lindgren</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103691457</v>
+        <v>129834381</v>
       </c>
       <c r="B5" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>43426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>100942</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1106,25 +1078,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Hinderbacken Yta 4:10 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505564.9043745915</v>
+        <v>505499</v>
       </c>
       <c r="R5" t="n">
-        <v>6611497.312694978</v>
+        <v>6611413</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1148,22 +1124,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,19 +1140,393 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129834383</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43426</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hinderbacken Yta 4:10 Ledningsgatan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505499</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611412</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ängsvädd</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Succisa pratensis</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>73727104</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Körartorp, 660 meter ost om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505420</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6611330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En av två växtplatser i närområdet.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anita Lindgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73727118</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Körartorp, 620 meter ost om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505378</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6611390</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anita Lindgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
